--- a/manufacturing_forms/018_storage_humidity_control_report_form--manufacturing_forms.xlsx
+++ b/manufacturing_forms/018_storage_humidity_control_report_form--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_2.1,_'name':_6872}</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 2.1, 'name': 6872}</t>
+          <t>6872</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2.2,_'name':_7276}</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2.2, 'name': 7276}</t>
+          <t>7276</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_2.3,_'name':_7680}</t>
+          <t>7680</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 2.3, 'name': 7680}</t>
+          <t>7680</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_3.1,_'name':_60}</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 3.1, 'name': 60}</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3.2,_'name':_70}</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3.2, 'name': 70}</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3.3,_'name':_80}</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3.3, 'name': 80}</t>
+          <t>80</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3.4,_'name':_90}</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3.4, 'name': 90}</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8.1,_'name':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8.1, 'name': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_8.2,_'name':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 8.2, 'name': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_9.1,_'name':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 9.1, 'name': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_9.2,_'name':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 9.2, 'name': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_9.3,_'name':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 9.3, 'name': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_14.1,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 14.1, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_14.2,_'name':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 14.2, 'name': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_15.1,_'name':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 15.1, 'name': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_15.2,_'name':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 15.2, 'name': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_15.3,_'name':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 15.3, 'name': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
